--- a/2026電商激勵活動rundown+主持稿_寶原.xlsx
+++ b/2026電商激勵活動rundown+主持稿_寶原.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Devin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8001_{DC56F1A0-964D-4662-8237-560864BA40B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364A89F0-34D5-42A2-8D74-FB14E47C5376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33017" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="907" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="907" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="活動流程表" sheetId="21" r:id="rId1"/>
@@ -32,8 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -135,10 +133,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>0800-0900</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>下車區</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -162,10 +156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1510-1520</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>各處誓師表演</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -235,19 +225,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1520-1530</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1530-1535</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>空拍+大合照</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1625-1630</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -643,42 +621,10 @@
     <t>抵達會場後先帶上耳麥和call機</t>
   </si>
   <si>
-    <t>0940-0950</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0950-0953</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0953-1003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1003-1008</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1008-1018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1018-1118</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>轉場</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1118-1120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1120-1158</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SUP區</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -695,19 +641,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1158-1238</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>確認餐點</t>
-  </si>
-  <si>
-    <t>1238-1248</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1248-1308</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SUP決賽6組</t>
@@ -719,27 +653,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1308-1318</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1318-1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1500-1510</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>頒獎典禮</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>誓師大會</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1615-1625</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -869,14 +787,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1555-1615</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1535-1555</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.確認並清點設計物道具收回
 2.確認主會場、烤肉區、SUP競賽區等是否有物品遺落、momo工作人員物品收回。
 3.確認飲料/飲用水剩餘數量</t>
@@ -1086,10 +996,6 @@
   </si>
   <si>
     <t>主持文稿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0910-0940</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2870,6 +2776,98 @@
       <t>27</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0801-0900</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0901-0940</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0941-0950</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0951-0953</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0954-1003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004-1008</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1009-1018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1019-1118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1119-1120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1121-1158</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1159-1238</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1239-1248</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1249-1308</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1309-1318</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1319-1500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1501-1510</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1511-1520</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1521-1530</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1531-1535</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1536-1555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1556-1615</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1616-1625</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1626-1630</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3825,6 +3823,30 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3843,311 +3865,287 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4470,11 +4468,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="30" customHeight="1">
-      <c r="B1" s="106" t="s">
-        <v>118</v>
-      </c>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
+      <c r="B1" s="107" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
     </row>
     <row r="2" spans="2:4" ht="14.4" customHeight="1">
       <c r="B2" s="15"/>
@@ -4483,14 +4481,14 @@
     </row>
     <row r="3" spans="2:4" ht="18.45">
       <c r="B3" s="16" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
     </row>
     <row r="4" spans="2:4" ht="18.45">
       <c r="B4" s="16" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -4498,222 +4496,222 @@
     <row r="5" spans="2:4" ht="17.149999999999999" thickBot="1"/>
     <row r="6" spans="2:4" ht="21" customHeight="1" thickBot="1">
       <c r="B6" s="26" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="24" customHeight="1">
       <c r="B7" s="95" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="24" customHeight="1">
       <c r="B8" s="96" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="24" customHeight="1">
       <c r="B9" s="97" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="24" customHeight="1">
       <c r="B10" s="96" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="24" customHeight="1">
       <c r="B11" s="97" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="24" customHeight="1">
       <c r="B12" s="96" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="24" customHeight="1">
       <c r="B13" s="97" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="24" customHeight="1">
       <c r="B14" s="96" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="24" customHeight="1">
       <c r="B15" s="97" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="24" customHeight="1">
       <c r="B16" s="96" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="24" customHeight="1">
       <c r="B17" s="97" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="24" customHeight="1">
       <c r="B18" s="96" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="24" customHeight="1">
       <c r="B19" s="97" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="24" customHeight="1">
       <c r="B20" s="96" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="24" customHeight="1">
       <c r="B21" s="17" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="24" customHeight="1">
       <c r="B22" s="20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="24" customHeight="1">
       <c r="B23" s="17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="24" customHeight="1">
       <c r="B24" s="20" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="24" customHeight="1">
       <c r="B25" s="17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="24" customHeight="1" thickBot="1">
@@ -4721,10 +4719,10 @@
         <v>0.6875</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5260,15 +5258,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" thickBot="1">
-      <c r="A1" s="109" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
+      <c r="A1" s="103" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
     </row>
     <row r="2" spans="1:7" s="3" customFormat="1" ht="22.2" customHeight="1" thickBot="1">
       <c r="A2" s="69" t="s">
@@ -5287,7 +5285,7 @@
         <v>16</v>
       </c>
       <c r="F2" s="71" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G2" s="72" t="s">
         <v>1</v>
@@ -5295,19 +5293,19 @@
     </row>
     <row r="3" spans="1:7" s="3" customFormat="1" ht="24.65" customHeight="1">
       <c r="A3" s="66" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D3" s="67" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F3" s="67"/>
       <c r="G3" s="68"/>
@@ -5323,85 +5321,85 @@
         <v>11</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="53" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="253.5" customHeight="1">
-      <c r="A5" s="110" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="111" t="s">
+      <c r="A5" s="104" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" s="105" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="F5" s="47"/>
-      <c r="G5" s="112" t="s">
-        <v>359</v>
+      <c r="G5" s="106" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="114.65" customHeight="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="111"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="105"/>
       <c r="C6" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="F6" s="12"/>
-      <c r="G6" s="112"/>
+      <c r="G6" s="106"/>
     </row>
     <row r="7" spans="1:7" ht="160.94999999999999" customHeight="1">
-      <c r="A7" s="110"/>
-      <c r="B7" s="111"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="105"/>
       <c r="C7" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="112"/>
+      <c r="G7" s="106"/>
     </row>
     <row r="8" spans="1:7" ht="66" customHeight="1">
-      <c r="A8" s="110"/>
-      <c r="B8" s="111"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="105"/>
       <c r="C8" s="12" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="112"/>
+      <c r="G8" s="106"/>
     </row>
     <row r="9" spans="1:7" ht="135" customHeight="1">
       <c r="A9" s="54" t="s">
-        <v>231</v>
+        <v>356</v>
       </c>
       <c r="B9" s="43" t="s">
         <v>17</v>
@@ -5410,10 +5408,10 @@
         <v>11</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="55" t="s">
@@ -5421,776 +5419,770 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="42.45" customHeight="1">
-      <c r="A10" s="113" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="107" t="s">
+      <c r="A10" s="101" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="100" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="E10" s="73" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="55" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="42.45" customHeight="1">
-      <c r="A11" s="113"/>
-      <c r="B11" s="107"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="100"/>
       <c r="C11" s="45" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="E11" s="73" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="94" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="98.4" customHeight="1">
-      <c r="A12" s="113"/>
-      <c r="B12" s="107"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="100"/>
       <c r="C12" s="45" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="E12" s="73" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="84" customHeight="1">
       <c r="A13" s="57" t="s">
-        <v>146</v>
+        <v>358</v>
       </c>
       <c r="B13" s="45" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E13" s="73" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="F13" s="45" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="G13" s="55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="44.4" customHeight="1">
-      <c r="A14" s="108" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="107" t="s">
+      <c r="A14" s="102" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="100" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="E14" s="73" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="G14" s="58"/>
     </row>
     <row r="15" spans="1:7" ht="41.4" customHeight="1">
-      <c r="A15" s="108"/>
-      <c r="B15" s="107"/>
+      <c r="A15" s="102"/>
+      <c r="B15" s="100"/>
       <c r="C15" s="45" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="E15" s="93"/>
       <c r="F15" s="45" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="G15" s="94"/>
     </row>
     <row r="16" spans="1:7" ht="61.95" customHeight="1">
-      <c r="A16" s="108" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="107" t="s">
+      <c r="A16" s="102" t="s">
+        <v>360</v>
+      </c>
+      <c r="B16" s="100" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="55" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="54" customHeight="1">
-      <c r="A17" s="108"/>
-      <c r="B17" s="107"/>
+      <c r="A17" s="102"/>
+      <c r="B17" s="100"/>
       <c r="C17" s="45" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="E17" s="73" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="F17" s="45" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="G17" s="94"/>
     </row>
     <row r="18" spans="1:7" ht="105" customHeight="1">
       <c r="A18" s="57" t="s">
-        <v>149</v>
+        <v>361</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="94" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="139.85" customHeight="1">
-      <c r="A19" s="113" t="s">
-        <v>150</v>
+      <c r="A19" s="101" t="s">
+        <v>362</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="93" customHeight="1">
-      <c r="A20" s="113"/>
+      <c r="A20" s="101"/>
       <c r="B20" s="45" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="45.45" customHeight="1">
-      <c r="A21" s="113"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="45" t="s">
-        <v>198</v>
-      </c>
-      <c r="D21" s="44" t="s">
-        <v>27</v>
-      </c>
       <c r="E21" s="45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="94" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="64.5" customHeight="1">
       <c r="A22" s="56" t="s">
-        <v>152</v>
+        <v>363</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="55"/>
     </row>
     <row r="23" spans="1:7" ht="48" customHeight="1">
-      <c r="A23" s="108" t="s">
-        <v>153</v>
-      </c>
-      <c r="B23" s="107" t="s">
-        <v>179</v>
+      <c r="A23" s="102" t="s">
+        <v>364</v>
+      </c>
+      <c r="B23" s="100" t="s">
+        <v>159</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="58.2" customHeight="1">
-      <c r="A24" s="108"/>
-      <c r="B24" s="107"/>
+      <c r="A24" s="102"/>
+      <c r="B24" s="100"/>
       <c r="C24" s="45" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="100.95" customHeight="1">
-      <c r="A25" s="108"/>
-      <c r="B25" s="107"/>
+      <c r="A25" s="102"/>
+      <c r="B25" s="100"/>
       <c r="C25" s="45" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="49.2" customHeight="1">
-      <c r="A26" s="113" t="s">
-        <v>158</v>
-      </c>
-      <c r="B26" s="107" t="s">
-        <v>180</v>
+      <c r="A26" s="101" t="s">
+        <v>365</v>
+      </c>
+      <c r="B26" s="100" t="s">
+        <v>160</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="51.65" customHeight="1">
-      <c r="A27" s="113"/>
-      <c r="B27" s="107"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="100"/>
       <c r="C27" s="45" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="101.6" customHeight="1">
-      <c r="A28" s="113"/>
-      <c r="B28" s="107"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="100"/>
       <c r="C28" s="45" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="48" customHeight="1">
-      <c r="A29" s="113"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="45" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="55" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="108" customHeight="1">
-      <c r="A30" s="113"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="45" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="55" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="96" customHeight="1">
       <c r="A31" s="56" t="s">
-        <v>160</v>
+        <v>366</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="66" customHeight="1">
-      <c r="A32" s="113" t="s">
-        <v>161</v>
+      <c r="A32" s="101" t="s">
+        <v>367</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="84.45" customHeight="1">
-      <c r="A33" s="113"/>
-      <c r="B33" s="107" t="s">
-        <v>162</v>
+      <c r="A33" s="101"/>
+      <c r="B33" s="100" t="s">
+        <v>146</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="105" customHeight="1">
-      <c r="A34" s="113"/>
-      <c r="B34" s="107"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="100"/>
       <c r="C34" s="45" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="56.4" customHeight="1">
-      <c r="A35" s="113"/>
+      <c r="A35" s="101"/>
       <c r="B35" s="45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="55" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="108" customHeight="1">
       <c r="A36" s="60" t="s">
-        <v>164</v>
+        <v>368</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="55" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="72" customHeight="1">
-      <c r="A37" s="113" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="107" t="s">
-        <v>186</v>
+      <c r="A37" s="101" t="s">
+        <v>369</v>
+      </c>
+      <c r="B37" s="100" t="s">
+        <v>166</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="55" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="203.4" customHeight="1">
-      <c r="A38" s="113"/>
-      <c r="B38" s="107"/>
+      <c r="A38" s="101"/>
+      <c r="B38" s="100"/>
       <c r="C38" s="45" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="D38" s="44" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="55" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="87" customHeight="1">
       <c r="A39" s="57" t="s">
-        <v>166</v>
+        <v>370</v>
       </c>
       <c r="B39" s="45" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="45" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D39" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="E39" s="45" t="s">
         <v>310</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>333</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="55" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="109.85" customHeight="1">
       <c r="A40" s="57" t="s">
-        <v>28</v>
+        <v>371</v>
       </c>
       <c r="B40" s="45" t="s">
         <v>20</v>
       </c>
       <c r="C40" s="45" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D40" s="44" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="E40" s="45" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="F40" s="45" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="G40" s="55" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="120" customHeight="1">
-      <c r="A41" s="113" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="107" t="s">
-        <v>167</v>
-      </c>
-      <c r="C41" s="107" t="s">
-        <v>198</v>
+      <c r="A41" s="101" t="s">
+        <v>372</v>
+      </c>
+      <c r="B41" s="100" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="100" t="s">
+        <v>176</v>
       </c>
       <c r="D41" s="44" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="E41" s="45" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="F41" s="45" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="G41" s="55" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="37.85" customHeight="1">
-      <c r="A42" s="113"/>
-      <c r="B42" s="107"/>
-      <c r="C42" s="107"/>
+      <c r="A42" s="101"/>
+      <c r="B42" s="100"/>
+      <c r="C42" s="100"/>
       <c r="D42" s="44" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E42" s="48"/>
       <c r="F42" s="8"/>
       <c r="G42" s="55" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="84" customHeight="1">
       <c r="A43" s="57" t="s">
-        <v>47</v>
+        <v>373</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="C43" s="45" t="s">
         <v>2</v>
       </c>
       <c r="D43" s="44" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="E43" s="45" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="55" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="102.65" customHeight="1">
       <c r="A44" s="57" t="s">
-        <v>193</v>
+        <v>374</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C44" s="45" t="s">
         <v>2</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="F44" s="45"/>
       <c r="G44" s="55" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="93.65" customHeight="1">
       <c r="A45" s="60" t="s">
-        <v>192</v>
+        <v>375</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C45" s="45" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="E45" s="45" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="F45" s="45" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="G45" s="59"/>
     </row>
     <row r="46" spans="1:7" ht="138" customHeight="1">
       <c r="A46" s="60" t="s">
-        <v>169</v>
+        <v>376</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C46" s="45" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="F46" s="45" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="G46" s="55" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="120" customHeight="1">
       <c r="A47" s="60" t="s">
-        <v>49</v>
+        <v>377</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="E47" s="45" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="55" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="65.599999999999994" customHeight="1" thickBot="1">
       <c r="A48" s="61">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B48" s="62" t="s">
         <v>19</v>
       </c>
       <c r="C48" s="62" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D48" s="63" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="F48" s="64"/>
       <c r="G48" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
     <mergeCell ref="C41:C42"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="B23:B25"/>
@@ -6207,6 +6199,12 @@
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6230,385 +6228,385 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="9" customFormat="1" ht="42.65" customHeight="1" thickBot="1">
-      <c r="A1" s="100" t="s">
-        <v>228</v>
-      </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="108" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" ht="24" customHeight="1" thickBot="1">
       <c r="A2" s="77" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" s="79" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" ht="29.4" customHeight="1">
       <c r="A3" s="80" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" ht="29.4" customHeight="1">
       <c r="A4" s="83" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" ht="29.4" customHeight="1">
       <c r="A5" s="83" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" s="74" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="84" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="321" customHeight="1">
       <c r="A6" s="83" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="B6" s="74" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" s="84" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="62.4" customHeight="1">
       <c r="A7" s="83" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="C7" s="84" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="216" customHeight="1">
-      <c r="A8" s="101" t="s">
-        <v>235</v>
+      <c r="A8" s="109" t="s">
+        <v>212</v>
       </c>
       <c r="B8" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="84" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="40.950000000000003" customHeight="1">
+      <c r="A9" s="109"/>
+      <c r="B9" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="84" t="s">
         <v>34</v>
-      </c>
-      <c r="C8" s="84" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="40.950000000000003" customHeight="1">
-      <c r="A9" s="101"/>
-      <c r="B9" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="84" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="243" customHeight="1">
       <c r="A10" s="85" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="C10" s="84" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="294.64999999999998" customHeight="1">
       <c r="A11" s="83" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B11" s="75" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="C11" s="84" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="375" customHeight="1">
       <c r="A12" s="83" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="B12" s="75" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="C12" s="84" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="409.6" customHeight="1">
       <c r="A13" s="83" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="C13" s="84" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="180" customHeight="1">
       <c r="A14" s="83" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="B14" s="75" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="C14" s="84" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="206.4" customHeight="1">
       <c r="A15" s="83" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="B15" s="75" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="C15" s="84" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="205.2" customHeight="1">
       <c r="A16" s="83" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="B16" s="75" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="C16" s="84" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="291.64999999999998" customHeight="1">
       <c r="A17" s="83" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="B17" s="75" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C17" s="84" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="268.2" customHeight="1">
       <c r="A18" s="83" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="B18" s="75" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="C18" s="84" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="297" customHeight="1">
       <c r="A19" s="83" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="B19" s="75" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="C19" s="84" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="386.4" customHeight="1">
       <c r="A20" s="83" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="B20" s="75" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="C20" s="84" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="316.95" customHeight="1">
-      <c r="A21" s="102" t="s">
-        <v>256</v>
-      </c>
-      <c r="B21" s="104" t="s">
-        <v>252</v>
+      <c r="A21" s="110" t="s">
+        <v>233</v>
+      </c>
+      <c r="B21" s="112" t="s">
+        <v>229</v>
       </c>
       <c r="C21" s="84" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="25.85" customHeight="1">
-      <c r="A22" s="103"/>
-      <c r="B22" s="105"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="113"/>
       <c r="C22" s="84" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="234.65" customHeight="1">
       <c r="A23" s="83" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="B23" s="74" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="C23" s="84" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="283.85000000000002" customHeight="1">
       <c r="A24" s="83" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="B24" s="75" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="C24" s="84" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="49.85" customHeight="1">
       <c r="A25" s="83" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="B25" s="75" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="C25" s="98" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60.65" customHeight="1">
-      <c r="A26" s="102" t="s">
-        <v>265</v>
-      </c>
-      <c r="B26" s="104" t="s">
-        <v>264</v>
+      <c r="A26" s="110" t="s">
+        <v>242</v>
+      </c>
+      <c r="B26" s="112" t="s">
+        <v>241</v>
       </c>
       <c r="C26" s="84" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="71.400000000000006" customHeight="1">
-      <c r="A27" s="103"/>
-      <c r="B27" s="105"/>
+      <c r="A27" s="111"/>
+      <c r="B27" s="113"/>
       <c r="C27" s="84" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="80.400000000000006" customHeight="1">
       <c r="A28" s="83" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="B28" s="76" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="C28" s="84" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="90" customHeight="1">
       <c r="A29" s="83" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="B29" s="75" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="C29" s="84" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="409.6" customHeight="1">
       <c r="A30" s="83" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B30" s="74" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C30" s="84" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="47.4" customHeight="1">
       <c r="A31" s="86" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="B31" s="74" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="C31" s="84" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="385.85" customHeight="1">
       <c r="A32" s="87" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B32" s="88" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C32" s="84" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="136.85" customHeight="1">
       <c r="A33" s="85" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B33" s="91" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="C33" s="84" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="281.39999999999998" customHeight="1">
       <c r="A34" s="83" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="B34" s="75" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C34" s="84" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="249" customHeight="1">
       <c r="A35" s="83" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="B35" s="75" t="s">
         <v>3</v>
       </c>
       <c r="C35" s="84" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="79.95" customHeight="1" thickBot="1">
       <c r="A36" s="89" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" s="90" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C36" s="99" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6651,98 +6649,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46">
-      <c r="S1" s="114" t="s">
-        <v>121</v>
-      </c>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
-      <c r="AC1" s="114"/>
+      <c r="S1" s="207" t="s">
+        <v>116</v>
+      </c>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
+      <c r="Y1" s="207"/>
+      <c r="Z1" s="207"/>
+      <c r="AA1" s="207"/>
+      <c r="AB1" s="207"/>
+      <c r="AC1" s="207"/>
     </row>
     <row r="2" spans="2:46">
-      <c r="S2" s="114"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="114"/>
-      <c r="V2" s="114"/>
-      <c r="W2" s="114"/>
-      <c r="X2" s="114"/>
-      <c r="Y2" s="114"/>
-      <c r="Z2" s="114"/>
-      <c r="AA2" s="114"/>
-      <c r="AB2" s="114"/>
-      <c r="AC2" s="114"/>
+      <c r="S2" s="207"/>
+      <c r="T2" s="207"/>
+      <c r="U2" s="207"/>
+      <c r="V2" s="207"/>
+      <c r="W2" s="207"/>
+      <c r="X2" s="207"/>
+      <c r="Y2" s="207"/>
+      <c r="Z2" s="207"/>
+      <c r="AA2" s="207"/>
+      <c r="AB2" s="207"/>
+      <c r="AC2" s="207"/>
     </row>
     <row r="5" spans="2:46" ht="17.149999999999999" thickBot="1">
       <c r="B5" s="29"/>
       <c r="C5" s="115" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D5" s="115"/>
       <c r="E5" s="29"/>
-      <c r="F5" s="116" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
+      <c r="F5" s="114" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
       <c r="I5" s="115" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J5" s="115"/>
       <c r="K5" s="115"/>
-      <c r="L5" s="116" t="s">
-        <v>125</v>
-      </c>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
+      <c r="L5" s="114" t="s">
+        <v>120</v>
+      </c>
+      <c r="M5" s="114"/>
+      <c r="N5" s="114"/>
+      <c r="O5" s="114"/>
       <c r="P5" s="29"/>
       <c r="Q5" s="115" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="R5" s="115"/>
       <c r="S5" s="29"/>
-      <c r="T5" s="116" t="s">
+      <c r="T5" s="114" t="s">
+        <v>122</v>
+      </c>
+      <c r="U5" s="114"/>
+      <c r="V5" s="114"/>
+      <c r="W5" s="114" t="s">
+        <v>123</v>
+      </c>
+      <c r="X5" s="114"/>
+      <c r="Y5" s="114"/>
+      <c r="Z5" s="114" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA5" s="114"/>
+      <c r="AB5" s="114"/>
+      <c r="AC5" s="114" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD5" s="114"/>
+      <c r="AE5" s="114"/>
+      <c r="AF5" s="114"/>
+      <c r="AG5" s="114" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH5" s="114"/>
+      <c r="AI5" s="114"/>
+      <c r="AJ5" s="114"/>
+      <c r="AK5" s="114" t="s">
         <v>127</v>
       </c>
-      <c r="U5" s="116"/>
-      <c r="V5" s="116"/>
-      <c r="W5" s="116" t="s">
+      <c r="AL5" s="114"/>
+      <c r="AM5" s="114"/>
+      <c r="AN5" s="114"/>
+      <c r="AO5" s="114"/>
+      <c r="AP5" s="115" t="s">
         <v>128</v>
-      </c>
-      <c r="X5" s="116"/>
-      <c r="Y5" s="116"/>
-      <c r="Z5" s="116" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA5" s="116"/>
-      <c r="AB5" s="116"/>
-      <c r="AC5" s="116" t="s">
-        <v>130</v>
-      </c>
-      <c r="AD5" s="116"/>
-      <c r="AE5" s="116"/>
-      <c r="AF5" s="116"/>
-      <c r="AG5" s="116" t="s">
-        <v>131</v>
-      </c>
-      <c r="AH5" s="116"/>
-      <c r="AI5" s="116"/>
-      <c r="AJ5" s="116"/>
-      <c r="AK5" s="116" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL5" s="116"/>
-      <c r="AM5" s="116"/>
-      <c r="AN5" s="116"/>
-      <c r="AO5" s="116"/>
-      <c r="AP5" s="115" t="s">
-        <v>133</v>
       </c>
       <c r="AQ5" s="115"/>
       <c r="AR5" s="115"/>
@@ -6750,169 +6748,169 @@
       <c r="AT5" s="115"/>
     </row>
     <row r="6" spans="2:46" ht="18" customHeight="1">
-      <c r="B6" s="117" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="123" t="s">
-        <v>282</v>
-      </c>
-      <c r="G6" s="124"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="132" t="s">
-        <v>377</v>
-      </c>
-      <c r="J6" s="132"/>
-      <c r="K6" s="132"/>
-      <c r="L6" s="135" t="s">
-        <v>283</v>
-      </c>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="137"/>
-      <c r="P6" s="144" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q6" s="145"/>
-      <c r="R6" s="145"/>
-      <c r="S6" s="145"/>
-      <c r="T6" s="148" t="s">
-        <v>284</v>
-      </c>
-      <c r="U6" s="149"/>
-      <c r="V6" s="150"/>
-      <c r="W6" s="157" t="s">
-        <v>285</v>
-      </c>
-      <c r="X6" s="158"/>
-      <c r="Y6" s="159"/>
-      <c r="Z6" s="166" t="s">
-        <v>286</v>
-      </c>
-      <c r="AA6" s="167"/>
-      <c r="AB6" s="167"/>
-      <c r="AC6" s="172" t="s">
-        <v>287</v>
-      </c>
-      <c r="AD6" s="173"/>
-      <c r="AE6" s="173"/>
-      <c r="AF6" s="174"/>
-      <c r="AG6" s="181" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH6" s="182"/>
-      <c r="AI6" s="182"/>
-      <c r="AJ6" s="183"/>
-      <c r="AK6" s="190" t="s">
-        <v>376</v>
-      </c>
-      <c r="AL6" s="191"/>
-      <c r="AM6" s="191"/>
-      <c r="AN6" s="191"/>
-      <c r="AO6" s="192"/>
-      <c r="AP6" s="199" t="s">
-        <v>288</v>
-      </c>
-      <c r="AQ6" s="200"/>
-      <c r="AR6" s="200"/>
-      <c r="AS6" s="200"/>
-      <c r="AT6" s="201"/>
+      <c r="B6" s="116" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="122" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="123"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="131" t="s">
+        <v>354</v>
+      </c>
+      <c r="J6" s="131"/>
+      <c r="K6" s="131"/>
+      <c r="L6" s="134" t="s">
+        <v>260</v>
+      </c>
+      <c r="M6" s="135"/>
+      <c r="N6" s="135"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="143" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q6" s="144"/>
+      <c r="R6" s="144"/>
+      <c r="S6" s="144"/>
+      <c r="T6" s="147" t="s">
+        <v>261</v>
+      </c>
+      <c r="U6" s="148"/>
+      <c r="V6" s="149"/>
+      <c r="W6" s="156" t="s">
+        <v>262</v>
+      </c>
+      <c r="X6" s="157"/>
+      <c r="Y6" s="158"/>
+      <c r="Z6" s="165" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA6" s="166"/>
+      <c r="AB6" s="166"/>
+      <c r="AC6" s="171" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD6" s="172"/>
+      <c r="AE6" s="172"/>
+      <c r="AF6" s="173"/>
+      <c r="AG6" s="180" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH6" s="181"/>
+      <c r="AI6" s="181"/>
+      <c r="AJ6" s="182"/>
+      <c r="AK6" s="189" t="s">
+        <v>353</v>
+      </c>
+      <c r="AL6" s="190"/>
+      <c r="AM6" s="190"/>
+      <c r="AN6" s="190"/>
+      <c r="AO6" s="191"/>
+      <c r="AP6" s="198" t="s">
+        <v>265</v>
+      </c>
+      <c r="AQ6" s="199"/>
+      <c r="AR6" s="199"/>
+      <c r="AS6" s="199"/>
+      <c r="AT6" s="200"/>
     </row>
     <row r="7" spans="2:46" ht="18" customHeight="1">
-      <c r="B7" s="119"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="138"/>
-      <c r="M7" s="139"/>
-      <c r="N7" s="139"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="146"/>
-      <c r="Q7" s="146"/>
-      <c r="R7" s="146"/>
-      <c r="S7" s="146"/>
-      <c r="T7" s="151"/>
-      <c r="U7" s="152"/>
-      <c r="V7" s="153"/>
-      <c r="W7" s="160"/>
-      <c r="X7" s="161"/>
-      <c r="Y7" s="162"/>
-      <c r="Z7" s="168"/>
-      <c r="AA7" s="169"/>
-      <c r="AB7" s="169"/>
-      <c r="AC7" s="175"/>
-      <c r="AD7" s="176"/>
-      <c r="AE7" s="176"/>
-      <c r="AF7" s="177"/>
-      <c r="AG7" s="184"/>
-      <c r="AH7" s="185"/>
-      <c r="AI7" s="185"/>
-      <c r="AJ7" s="186"/>
-      <c r="AK7" s="193"/>
-      <c r="AL7" s="194"/>
-      <c r="AM7" s="194"/>
-      <c r="AN7" s="194"/>
-      <c r="AO7" s="195"/>
-      <c r="AP7" s="202"/>
-      <c r="AQ7" s="203"/>
-      <c r="AR7" s="203"/>
-      <c r="AS7" s="203"/>
-      <c r="AT7" s="204"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="137"/>
+      <c r="M7" s="138"/>
+      <c r="N7" s="138"/>
+      <c r="O7" s="139"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
+      <c r="R7" s="145"/>
+      <c r="S7" s="145"/>
+      <c r="T7" s="150"/>
+      <c r="U7" s="151"/>
+      <c r="V7" s="152"/>
+      <c r="W7" s="159"/>
+      <c r="X7" s="160"/>
+      <c r="Y7" s="161"/>
+      <c r="Z7" s="167"/>
+      <c r="AA7" s="168"/>
+      <c r="AB7" s="168"/>
+      <c r="AC7" s="174"/>
+      <c r="AD7" s="175"/>
+      <c r="AE7" s="175"/>
+      <c r="AF7" s="176"/>
+      <c r="AG7" s="183"/>
+      <c r="AH7" s="184"/>
+      <c r="AI7" s="184"/>
+      <c r="AJ7" s="185"/>
+      <c r="AK7" s="192"/>
+      <c r="AL7" s="193"/>
+      <c r="AM7" s="193"/>
+      <c r="AN7" s="193"/>
+      <c r="AO7" s="194"/>
+      <c r="AP7" s="201"/>
+      <c r="AQ7" s="202"/>
+      <c r="AR7" s="202"/>
+      <c r="AS7" s="202"/>
+      <c r="AT7" s="203"/>
     </row>
     <row r="8" spans="2:46" ht="18" customHeight="1" thickBot="1">
-      <c r="B8" s="121"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="128"/>
-      <c r="I8" s="134"/>
-      <c r="J8" s="134"/>
-      <c r="K8" s="134"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="147"/>
-      <c r="Q8" s="147"/>
-      <c r="R8" s="147"/>
-      <c r="S8" s="147"/>
-      <c r="T8" s="151"/>
-      <c r="U8" s="152"/>
-      <c r="V8" s="153"/>
-      <c r="W8" s="163"/>
-      <c r="X8" s="164"/>
-      <c r="Y8" s="165"/>
-      <c r="Z8" s="170"/>
-      <c r="AA8" s="171"/>
-      <c r="AB8" s="171"/>
-      <c r="AC8" s="178"/>
-      <c r="AD8" s="179"/>
-      <c r="AE8" s="179"/>
-      <c r="AF8" s="180"/>
-      <c r="AG8" s="187"/>
-      <c r="AH8" s="188"/>
-      <c r="AI8" s="188"/>
-      <c r="AJ8" s="189"/>
-      <c r="AK8" s="193"/>
-      <c r="AL8" s="194"/>
-      <c r="AM8" s="194"/>
-      <c r="AN8" s="194"/>
-      <c r="AO8" s="195"/>
-      <c r="AP8" s="205"/>
-      <c r="AQ8" s="206"/>
-      <c r="AR8" s="206"/>
-      <c r="AS8" s="206"/>
-      <c r="AT8" s="207"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="137"/>
+      <c r="M8" s="138"/>
+      <c r="N8" s="138"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="146"/>
+      <c r="Q8" s="146"/>
+      <c r="R8" s="146"/>
+      <c r="S8" s="146"/>
+      <c r="T8" s="150"/>
+      <c r="U8" s="151"/>
+      <c r="V8" s="152"/>
+      <c r="W8" s="162"/>
+      <c r="X8" s="163"/>
+      <c r="Y8" s="164"/>
+      <c r="Z8" s="169"/>
+      <c r="AA8" s="170"/>
+      <c r="AB8" s="170"/>
+      <c r="AC8" s="177"/>
+      <c r="AD8" s="178"/>
+      <c r="AE8" s="178"/>
+      <c r="AF8" s="179"/>
+      <c r="AG8" s="186"/>
+      <c r="AH8" s="187"/>
+      <c r="AI8" s="187"/>
+      <c r="AJ8" s="188"/>
+      <c r="AK8" s="192"/>
+      <c r="AL8" s="193"/>
+      <c r="AM8" s="193"/>
+      <c r="AN8" s="193"/>
+      <c r="AO8" s="194"/>
+      <c r="AP8" s="204"/>
+      <c r="AQ8" s="205"/>
+      <c r="AR8" s="205"/>
+      <c r="AS8" s="205"/>
+      <c r="AT8" s="206"/>
     </row>
     <row r="9" spans="2:46" ht="18" customHeight="1" thickBot="1">
       <c r="B9" s="7">
@@ -6927,9 +6925,9 @@
       <c r="E9" s="7">
         <v>4</v>
       </c>
-      <c r="F9" s="129"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="131"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="130"/>
       <c r="I9" s="7">
         <v>1</v>
       </c>
@@ -6939,10 +6937,10 @@
       <c r="K9" s="7">
         <v>3</v>
       </c>
-      <c r="L9" s="141"/>
-      <c r="M9" s="142"/>
-      <c r="N9" s="142"/>
-      <c r="O9" s="143"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="141"/>
+      <c r="N9" s="141"/>
+      <c r="O9" s="142"/>
       <c r="P9" s="7">
         <v>1</v>
       </c>
@@ -6955,9 +6953,9 @@
       <c r="S9" s="7">
         <v>4</v>
       </c>
-      <c r="T9" s="154"/>
-      <c r="U9" s="155"/>
-      <c r="V9" s="156"/>
+      <c r="T9" s="153"/>
+      <c r="U9" s="154"/>
+      <c r="V9" s="155"/>
       <c r="W9" s="7">
         <v>1</v>
       </c>
@@ -7000,11 +6998,11 @@
       <c r="AJ9" s="7">
         <v>4</v>
       </c>
-      <c r="AK9" s="196"/>
-      <c r="AL9" s="197"/>
-      <c r="AM9" s="197"/>
-      <c r="AN9" s="197"/>
-      <c r="AO9" s="198"/>
+      <c r="AK9" s="195"/>
+      <c r="AL9" s="196"/>
+      <c r="AM9" s="196"/>
+      <c r="AN9" s="196"/>
+      <c r="AO9" s="197"/>
       <c r="AP9" s="7">
         <v>1</v>
       </c>
@@ -8323,11 +8321,21 @@
     </row>
     <row r="25" spans="2:46">
       <c r="B25" s="29" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="S1:AC2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="W5:Y5"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="AC5:AF5"/>
+    <mergeCell ref="F5:H5"/>
     <mergeCell ref="AG5:AJ5"/>
     <mergeCell ref="AK5:AO5"/>
     <mergeCell ref="AP5:AT5"/>
@@ -8343,16 +8351,6 @@
     <mergeCell ref="AG6:AJ8"/>
     <mergeCell ref="AK6:AO9"/>
     <mergeCell ref="AP6:AT8"/>
-    <mergeCell ref="S1:AC2"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="T5:V5"/>
-    <mergeCell ref="W5:Y5"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="AC5:AF5"/>
-    <mergeCell ref="F5:H5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
